--- a/outputs/Labour_Report_generated.xlsx
+++ b/outputs/Labour_Report_generated.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
-        <v>1160</v>
+        <v>710</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1130</v>
@@ -588,7 +588,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1160</v>
+        <v>710</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1130</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr"/>
       <c r="E4" s="3" t="n">
-        <v>393</v>
+        <v>303</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>333</v>
@@ -662,7 +662,7 @@
         <v>75</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>468</v>
+        <v>378</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>408</v>
@@ -705,39 +705,43 @@
       <c r="K5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>May 21</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="n">
-        <v>248</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>218</v>
-      </c>
-      <c r="G6" s="3" t="n">
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>455</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>278</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>248</v>
-      </c>
-      <c r="K6" s="3" t="inlineStr"/>
+      <c r="I6" s="2" t="n">
+        <v>395</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>485</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Oven &gt;6h</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -934,7 +938,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="n">
-        <v>640</v>
+        <v>520</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>625</v>
@@ -946,7 +950,7 @@
         <v>120</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>760</v>
+        <v>640</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>745</v>
@@ -1156,7 +1160,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="n">
-        <v>520</v>
+        <v>430</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>460</v>
@@ -1168,14 +1172,14 @@
         <v>75</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>595</v>
+        <v>505</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>535</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Bloor active &gt;8h | Oven &gt;6h</t>
+          <t>Oven &gt;6h</t>
         </is>
       </c>
     </row>
@@ -1215,39 +1219,43 @@
       <c r="K19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Jun 4</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="n">
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="I20" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>410</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>380</v>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Oven &gt;6h</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1363,43 +1371,39 @@
       <c r="K23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Jun 8</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>485</v>
-      </c>
-      <c r="G24" s="2" t="n">
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>345</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H24" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>520</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>505</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Bloor active &gt;8h | Oven &gt;6h</t>
-        </is>
-      </c>
+      <c r="I24" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>365</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1456,7 +1460,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="n">
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>420</v>
@@ -1468,7 +1472,7 @@
         <v>60</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>510</v>
+        <v>420</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>480</v>
@@ -1797,7 +1801,7 @@
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>480</v>
+        <v>30</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>480</v>
@@ -2431,7 +2435,7 @@
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>180</v>
@@ -2579,7 +2583,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
@@ -2617,7 +2621,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
@@ -3057,14 +3061,14 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>240</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>3</v>
+        <v>240</v>
       </c>
       <c r="H39" s="6" t="inlineStr"/>
     </row>
@@ -5055,7 +5059,7 @@
         </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>240</v>
@@ -7103,7 +7107,7 @@
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>180</v>
@@ -7733,14 +7737,14 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>240</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
@@ -9029,14 +9033,14 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="H12" s="6" t="inlineStr"/>
     </row>
@@ -9067,7 +9071,7 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>180</v>
@@ -10073,7 +10077,7 @@
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>180</v>

--- a/outputs/Labour_Report_generated.xlsx
+++ b/outputs/Labour_Report_generated.xlsx
@@ -909,16 +909,16 @@
         <v>85</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="K11" s="3" t="inlineStr"/>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="n">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>555</v>
@@ -1024,7 +1024,7 @@
         <v>45</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>600</v>
@@ -1051,10 +1051,10 @@
       </c>
       <c r="D15" s="3" t="inlineStr"/>
       <c r="E15" s="3" t="n">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>150</v>
@@ -1063,10 +1063,10 @@
         <v>150</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="K15" s="3" t="inlineStr"/>
     </row>
@@ -1371,39 +1371,43 @@
       <c r="K23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Jun 8</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="n">
-        <v>270</v>
-      </c>
-      <c r="F24" s="3" t="n">
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="F24" s="2" t="n">
+        <v>405</v>
+      </c>
+      <c r="G24" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="I24" s="3" t="n">
-        <v>290</v>
-      </c>
-      <c r="J24" s="3" t="n">
+      <c r="I24" s="2" t="n">
         <v>365</v>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="J24" s="2" t="n">
+        <v>425</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Oven &gt;6h</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1609,7 +1613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3258,33 +3262,29 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>NOTE</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Sausage &amp; Greens Pasta Sauce (→ Wk2 Sun Dinner)</t>
+          <t>Bean Salad (Fri Lunch)</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
+          <t>Rex</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr"/>
       <c r="F45" s="6" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Stove top</t>
+          <t>Cold salad pre-sent; no AM run needed</t>
         </is>
       </c>
     </row>
@@ -3296,122 +3296,122 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Sausage &amp; Greens Pasta Sauce (→ Wk2 Sun Dinner)</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Stove top</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>Reheat Pork/Chicken Adobo (Fri Dinner)</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F47" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="G46" s="6" t="n">
+      <c r="G47" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="6" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="H47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Pineapple Rice (Fri Dinner)</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F48" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="G48" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>⚠ NO RECIPE | Oven rice</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Steam Green Beans (Fri Dinner side)</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G48" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>Frozen; steam at Bloor</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
+          <t>Steam Green Beans (Fri Dinner side)</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -3421,18 +3421,18 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
         <v>15</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Reheat bagged</t>
+          <t>Frozen; steam at Bloor</t>
         </is>
       </c>
     </row>
@@ -3444,12 +3444,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Griot Marinade</t>
+          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -3459,18 +3459,18 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
         <v>15</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>For Griot Pork/Chicken/Tofu</t>
+          <t>Reheat bagged</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Cut/Marinate Pork Griot</t>
+          <t>Griot Marinade</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -3497,16 +3497,20 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="H51" s="6" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>For Griot Pork/Chicken/Tofu</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -3521,176 +3525,172 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
+          <t>Cut/Marinate Pork Griot</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
           <t>Marinate Chicken Griot</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F53" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="G52" s="6" t="n">
+      <c r="G53" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="H52" s="6" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="H53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F53" s="7" t="n">
+      <c r="F54" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G53" s="7" t="n">
+      <c r="G54" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="F55" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G54" s="6" t="n">
+      <c r="G55" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Carrot Cabbage Fry (Sat Dinner side)</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F55" s="7" t="n">
+      <c r="F56" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G55" s="7" t="n">
+      <c r="G56" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>Stir-fry at LAN; send hot PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
         </is>
       </c>
     </row>
@@ -3702,65 +3702,103 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F58" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G57" s="6" t="n">
+      <c r="G58" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="H57" s="6" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="H58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>ALT</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>🔸 BLAND ALT — Plain Chicken Leg (2 pcs) + Cabbage Stirfry + Plain Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F58" s="7" t="n">
+      <c r="F59" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G58" s="7" t="n">
+      <c r="G59" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H58" s="7" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>For bland/no-tomato/no-greens</t>
         </is>
@@ -3777,7 +3815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4657,40 +4695,40 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Reheat Pork Vindaloo (Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Coronation Chicken Salad Mix (→ Wed Lunch — make day before)</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F24" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
+      <c r="F24" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Mix; chill overnight; LAN holds</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4745,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Reheat Chicken Vindaloo — Halal (Tue Dinner)</t>
+          <t>Reheat Pork Vindaloo (Tue Dinner)</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -4717,7 +4755,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
@@ -4733,152 +4771,152 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Reheat Chicken Vindaloo — Halal (Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>ALT</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>🔸 BLAND ALT — Plain Chicken Leg (3 pcs) + Rice + Stirfry Veg (Tue Dinner)</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F27" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="G27" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>For GF/no-mustard/no-tomato/soft food</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Steamed Rice (Tue Dinner)</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F28" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G28" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>Oven rice</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Steam Broccoli (Tue Dinner side)</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="F29" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G29" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="H28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>ALT</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>🔸 GF ALT — Roasted Potatoes (small batch) for GF residents instead of Biscuit (Wed Lunch)</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>For 3-4 GF residents — replace biscuit with potato</t>
-        </is>
-      </c>
+      <c r="H29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -4888,33 +4926,29 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>NOTE</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Prep Griot Pork</t>
+          <t>Coronation Chicken Salad (Wed Lunch)</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>Rex</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr"/>
       <c r="F30" s="6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>RAW 1 bin/3 hotels</t>
+          <t>Cold salad pre-sent; no AM run needed</t>
         </is>
       </c>
     </row>
@@ -4926,12 +4960,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Prep Griot Chicken</t>
+          <t>🔸 GF ALT — Roasted Potatoes (small batch) for GF residents instead of Biscuit (Wed Lunch)</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -4941,18 +4975,18 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>RAW 1 bin/3 hotels</t>
+          <t>For 3-4 GF residents — replace biscuit with potato</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4998,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Beef Nacho Mix (→ Wk3 Tue Lunch)</t>
+          <t>Prep Griot Pork</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -4979,18 +5013,18 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Stove; cool; vac bag</t>
+          <t>RAW 1 bin/3 hotels</t>
         </is>
       </c>
     </row>
@@ -5002,12 +5036,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Vegan Nacho Mix (→ Wk3 Tue Lunch)</t>
+          <t>Prep Griot Chicken</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -5017,18 +5051,18 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Stove; cool; vac bag</t>
+          <t>RAW 1 bin/3 hotels</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5079,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Caribbean Stew</t>
+          <t>Beef Nacho Mix (→ Wk3 Tue Lunch)</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -5055,204 +5089,204 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
         <v>120</v>
       </c>
       <c r="G34" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Stove; cool; vac bag</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Vegan Nacho Mix (→ Wk3 Tue Lunch)</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Stove; cool; vac bag</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Caribbean Stew</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G36" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="H34" s="6" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Prep Chickpea Salad (→ Thu Lunch)</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F37" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="G37" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>Dress; chill; send Wed PM</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Chicken Ranch Salad Mix (→ Fri Lunch — make day before send)</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F38" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="G38" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>Mix; chill overnight; send Thu PM</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>Yetisse Fish (Wed Dinner)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F39" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G39" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>Bake; serve HOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Spiced Tofu (Wed Dinner — Veg)</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G38" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>Oven</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Coconut Rice &amp; Peas (Wed Dinner)</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>Oven rice</t>
         </is>
       </c>
     </row>
@@ -5264,12 +5298,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Reheat Eggplant/Cassava Stew (Wed Dinner)</t>
+          <t>Spiced Tofu (Wed Dinner — Veg)</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -5283,69 +5317,69 @@
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Reheat</t>
+          <t>Oven</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Halal Beef Burgers (Thu Lunch)</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>From freezer; oven 30 min day-of</t>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Coconut Rice &amp; Peas (Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Oven rice</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Black Bean Patties (Thu Lunch — Veg)</t>
+          <t>Reheat Eggplant/Cassava Stew (Wed Dinner)</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -5355,16 +5389,20 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
         <v>15</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="H42" s="6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Reheat</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -5379,7 +5417,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Pork Griot (→ Wk 3Thu Dinner)</t>
+          <t>Halal Beef Burgers (Thu Lunch)</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -5389,18 +5427,18 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Combi</t>
+          <t>From freezer; oven 30 min day-of</t>
         </is>
       </c>
     </row>
@@ -5417,218 +5455,214 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
+          <t>Black Bean Patties (Thu Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Pork Griot (→ Wk 3Thu Dinner)</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Combi</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
           <t>Chicken Griot — Halal option (→ Wk 3Thu Dinner)</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F46" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="G46" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="H44" s="6" t="inlineStr">
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>Oven</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>Tuna Rex Salad Mix (→ Sat Lunch — make day before)</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="G45" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>Mix; chill; send cold day-of</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>Chickpea Rex Salad (→ Sat Lunch — make day before)</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G46" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>Dress; chill; send cold</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Tuna Rex Salad Mix (→ Sat Lunch — make day before)</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>Mix; chill; send cold day-of</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Chickpea Rex Salad (→ Sat Lunch — make day before)</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>Dress; chill; send cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>Prep Slaw (→ Fri Lunch)</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F49" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="G49" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>Shred; dress; chill; send Thu PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Beef Sausages (Thu Dinner)</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G48" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>Cook sausages for dinner service</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Halal Sausages (Thu Dinner)</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>Cook sausages for dinner service</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5679,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Vegan Sausages (Thu Dinner)</t>
+          <t>Beef Sausages (Thu Dinner)</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -5683,7 +5717,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>HOT Peas &amp; Carrot → Dinner side</t>
+          <t>Halal Sausages (Thu Dinner)</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -5693,18 +5727,18 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Combi</t>
+          <t>Cook sausages for dinner service</t>
         </is>
       </c>
     </row>
@@ -5716,12 +5750,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Reheat Gravy (Thu Dinner + hold portion for Sat Dinner Meatloaf)</t>
+          <t>Vegan Sausages (Thu Dinner)</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -5735,21 +5769,21 @@
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Reheat bagged; portion ½ for Thu PM, hold ½ at Bloor for Sat</t>
+          <t>Cook sausages for dinner service</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -5759,7 +5793,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Beef CONC Salad Mix (→ Wk3 Sat Lunch)</t>
+          <t>HOT Peas &amp; Carrot → Dinner side</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -5769,94 +5803,94 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Cook; send Rex Sat PM; pull Wk3 Fri AM</t>
+          <t>Combi</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Reheat Gravy (Thu Dinner + hold portion for Sat Dinner Meatloaf)</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged; portion ½ for Thu PM, hold ½ at Bloor for Sat</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Vegan CONC Salad Mix (→ Wk3 Sat Lunch)</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Heat Falafel (frozen → oven) (Fri Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F54" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>Cook; send Rex Sat PM; pull Wk3 Fri AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>Prep Butternut Squash (→ Sat Dinner side)</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="G55" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>Peel/dice at LAN; chill overnight</t>
+      <c r="F55" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Purchased frozen; heat day-of at Bloor</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5902,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Prep &amp; Tray Meatloaf (raw) — 7 Beef (→ Sat Dinner)</t>
+          <t>Beef CONC Salad Mix (→ Wk3 Sat Lunch)</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -5883,18 +5917,18 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>Cook; send Rex Sat PM; pull Wk3 Fri AM</t>
         </is>
       </c>
     </row>
@@ -5906,12 +5940,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Prep &amp; Tray Vegan Meatloaf (raw) — (→ Sat Dinner)</t>
+          <t>Vegan CONC Salad Mix (→ Wk3 Sat Lunch)</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -5932,45 +5966,45 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>Cook; send Rex Sat PM; pull Wk3 Fri AM</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Reheat Refried Beans (Fri Dinner side)</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE — Reheat bagged</t>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>Prep Butternut Squash (→ Sat Dinner side)</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>Peel/dice at LAN; chill overnight</t>
         </is>
       </c>
     </row>
@@ -5982,12 +6016,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Arroz con Pollo</t>
+          <t>Prep &amp; Tray Meatloaf (raw) — 7 Beef (→ Sat Dinner)</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -5997,14 +6031,14 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F59" s="6" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>300</v>
+        <v>75</v>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
@@ -6013,85 +6047,85 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>Prep Roasted Peppers &amp; Onions (→ Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="G60" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Prep &amp; Tray Vegan Meatloaf (raw) — (→ Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>Tuna Salad Mix (→ Wk3 Mon Lunch)</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="G61" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>Mix; chill; send Sun PM</t>
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Reheat Refried Beans (Fri Dinner side)</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE — Reheat bagged</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -6101,7 +6135,7 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Beef Meatloaf — Bake (Sat Dinner)</t>
+          <t>Arroz con Pollo</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -6111,18 +6145,18 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F62" s="6" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Bake meatloaf from tray</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
     </row>
@@ -6134,67 +6168,67 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>NOTE</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Vegan Meatloaf — Bake (Sat Dinner)</t>
+          <t>Tuna Rex + Chickpea Rex Salad (Sat Lunch)</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>Rex</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr"/>
       <c r="F63" s="6" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="H63" s="6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Cold salad pre-sent; no AM run needed</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Roasted Potatoes (Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="G64" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>Prep Roasted Peppers &amp; Onions (→ Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
         </is>
       </c>
     </row>
@@ -6206,31 +6240,217 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>Tuna Salad Mix (→ Wk3 Mon Lunch)</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Mix; chill; send Sun PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Prep Broccoli Salad (→ Wk3 Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Make at Bloor; send PM to Rex</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Beef Meatloaf — Bake (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Bake meatloaf from tray</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Vegan Meatloaf — Bake (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="H68" s="6" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Roasted Potatoes (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G69" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>Roasted Butternut Squash (Sat Dinner side)</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F65" s="7" t="n">
+      <c r="F70" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G65" s="7" t="n">
+      <c r="G70" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="H70" s="7" t="inlineStr">
         <is>
           <t>Roast at LAN day-of</t>
         </is>
@@ -6247,7 +6467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7946,31 +8166,31 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>NOTE</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>White Chilli Chicken Pasta (→ Wk4 Sun Dinner)</t>
+          <t>Bean Salad (Fri Lunch)</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
+          <t>Rex</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr"/>
       <c r="F46" s="6" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="H46" s="6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Cold salad pre-sent; no AM run needed</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -7985,7 +8205,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Eggplant/Cassava Stew (→ Wk4 Wed Dinner)</t>
+          <t>White Chilli Chicken Pasta (→ Wk4 Sun Dinner)</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -7995,14 +8215,14 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="H47" s="6" t="inlineStr"/>
     </row>
@@ -8019,7 +8239,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Chicken &amp; Mushroom Fried Rice (Fri Dinner)</t>
+          <t>Eggplant/Cassava Stew (→ Wk4 Wed Dinner)</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -8029,20 +8249,16 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>Wok/oven</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="H48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -8057,7 +8273,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Vegan/No-Soy Mushroom Fried Rice (Fri Dinner — Veg)</t>
+          <t>Chicken &amp; Mushroom Fried Rice (Fri Dinner)</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -8067,14 +8283,14 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
@@ -8090,12 +8306,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Heat Spring Rolls (Fri Dinner side)</t>
+          <t>Vegan/No-Soy Mushroom Fried Rice (Fri Dinner — Veg)</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -8105,18 +8321,18 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Purchased frozen; heat day-of at Bloor</t>
+          <t>Wok/oven</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8344,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Bok Choy (Fri Dinner side)</t>
+          <t>Heat Spring Rolls (Fri Dinner side)</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -8143,35 +8359,35 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
         <v>15</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>⚠ NO RECIPE / amount unconfirmed — cook day-of at Bloor</t>
+          <t>Purchased frozen; heat day-of at Bloor</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
+          <t>Bok Choy (Fri Dinner side)</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -8181,18 +8397,18 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
         <v>15</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Reheat bagged</t>
+          <t>⚠ NO RECIPE / amount unconfirmed — cook day-of at Bloor</t>
         </is>
       </c>
     </row>
@@ -8204,12 +8420,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Cut/Season Tandoori Pork</t>
+          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -8223,14 +8439,14 @@
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Season w/Vindaloo Dry Spice Mix</t>
+          <t>Reheat bagged</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8463,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Tandoori Marinade</t>
+          <t>Cut/Season Tandoori Pork</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -8266,7 +8482,11 @@
       <c r="G54" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="H54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>Season w/Vindaloo Dry Spice Mix</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -8281,7 +8501,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Trim/Season BBQ Chicken Legs (→ Wk 4 Tuesday Dinner)</t>
+          <t>Tandoori Marinade</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -8291,21 +8511,21 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="H55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -8315,7 +8535,7 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Massaman Curry Paste</t>
+          <t>Trim/Season BBQ Chicken Legs (→ Wk 4 Tuesday Dinner)</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -8325,20 +8545,16 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOVED from Sat → Fri. Stores overnight in cambro. </t>
-        </is>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="H56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -8353,66 +8569,66 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
+          <t>Massaman Curry Paste</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOVED from Sat → Fri. Stores overnight in cambro. </t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
           <t>Portobello Cheese Melt prep (→ Wk4 Sun Lunch — Veg)</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F58" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G57" s="6" t="n">
+      <c r="G58" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>Prep/slice portobello; hold chilled; cook day-of</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="G58" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8645,7 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -8450,45 +8666,45 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
           <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G60" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
         </is>
       </c>
     </row>
@@ -8500,12 +8716,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Beef Massaman Curry (Sat Wk 4. Dinner)</t>
+          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -8515,18 +8731,18 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
-        <v>160</v>
+        <v>30</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>320</v>
+        <v>30</v>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Braised Beef (Combi) 2+ hours; Stove Top</t>
+          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
         </is>
       </c>
     </row>
@@ -8543,26 +8759,64 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
+          <t>Beef Massaman Curry (Sat Wk 4. Dinner)</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>320</v>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Braised Beef (Combi) 2+ hours; Stove Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
           <t>Potato Wedges (Sat Dinner side)</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F62" s="6" t="n">
+      <c r="F63" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="G62" s="6" t="n">
+      <c r="G63" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>Purchased frozen; oven</t>
         </is>
@@ -8579,7 +8833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9018,12 +9272,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Tandoori Pork (Wk. 4 Fri Dinner)</t>
+          <t>Reheat Vegan Chilli (Mon Lunch)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -9037,12 +9291,16 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -9052,185 +9310,181 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
+          <t>ALT</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>🔸 BLAND ALT — Plain Chicken Leg (3 pcs) + Rice + Stirfry Veg (Mon Lunch)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>For bland/no-chili restrictions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Tandoori Pork (Wk. 4 Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Chickpea Shakshuka</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F15" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G15" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">STOVE TOP (not Combi). Steam carrots 15m in Combi only. </t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Prep/Roast Peppers &amp; Onions (→ Tue Lunch — LAN day-of)</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Roast at LAN; send hot in AM van</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>Prep Mixed Greens (→ Tue Lunch side)</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F17" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G17" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>Prep at LAN; send cold Tue AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Cook Quinoa + Shape Quinoa Rice Cakes (→ Tue Lunch)</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Cook quinoa; combine; form cakes; chill overnight</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Cook Curry Fish (Mon Dinner)</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Fish 30min Combi</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9501,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Roast Curry Spiced Tofu (Mon Dinner — Veg)</t>
+          <t>Cook Quinoa + Shape Quinoa Rice Cakes (→ Tue Lunch)</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -9257,18 +9511,18 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>???</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Roast; send hot</t>
+          <t>Cook quinoa; combine; form cakes; chill overnight</t>
         </is>
       </c>
     </row>
@@ -9280,12 +9534,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Reheat Green Curry Sauce (Mon Dinner)</t>
+          <t>Cook Curry Fish (Mon Dinner)</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -9295,18 +9549,18 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Reheat bagged sauce</t>
+          <t>Fish 30min Combi</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9577,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Steam Green Beans (Mon Dinner side)</t>
+          <t>Roast Curry Spiced Tofu (Mon Dinner — Veg)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -9333,16 +9587,20 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="H20" s="6" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Roast; send hot</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -9352,12 +9610,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>ALT</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🔸 BLAND ALT — Plain Baked Fish (2 pcs, no onion) + Rice + Stirfry Veg (no beans) (Mon Dinner)</t>
+          <t>Reheat Green Curry Sauce (Mon Dinner)</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -9367,25 +9625,25 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>For no-curry/no-coconut/no-onion</t>
+          <t>Reheat bagged sauce</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -9395,7 +9653,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Beef/Halal Sausages (Tue Lunch)</t>
+          <t>Steam Green Beans (Mon Dinner side)</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -9405,35 +9663,31 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Oven/grill</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Vegan Sausages (Tue Lunch — Veg)</t>
+          <t>🔸 BLAND ALT — Plain Baked Fish (2 pcs, no onion) + Rice + Stirfry Veg (no beans) (Mon Dinner)</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -9443,18 +9697,18 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Roast</t>
+          <t>For no-curry/no-coconut/no-onion</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9725,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Crispy Quinoa Cakes (Tue Lunch — Veg alt)</t>
+          <t>Beef/Halal Sausages (Tue Lunch)</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -9492,7 +9746,7 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Pan fry</t>
+          <t>Oven/grill</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9763,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Tandoori Chicken — Halal (→ Fri Dinner)</t>
+          <t>Vegan Sausages (Tue Lunch — Veg)</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -9519,18 +9773,18 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Oven/Combi 1hr; bag</t>
+          <t>Roast</t>
         </is>
       </c>
     </row>
@@ -9547,7 +9801,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Butter Chicken (→ NC Wk1 Thu Dinner)</t>
+          <t>Crispy Quinoa Cakes (Tue Lunch — Veg alt)</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -9557,16 +9811,20 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="H26" s="6" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Pan fry</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -9581,7 +9839,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Butter Chickpeas (→ NC Wk1 Thu Dinner — Veg)</t>
+          <t>Tandoori Chicken — Halal (→ Fri Dinner)</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -9600,7 +9858,11 @@
       <c r="G27" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="H27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Oven/Combi 1hr; bag</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -9610,12 +9872,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Five-Spice Marinade (Thu Dinner)</t>
+          <t>Butter Chicken (→ NC Wk1 Thu Dinner)</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -9625,20 +9887,16 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Stove/Induction</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -9648,181 +9906,177 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Butter Chickpeas (→ NC Wk1 Thu Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Five-Spice Marinade (Thu Dinner)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Stove/Induction</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Season Teriyaki Chicken Legs (→ Thu Dinner)</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F31" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G31" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="H29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Coronation Chicken Salad Mix (→ Wed Lunch — make day before)</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F32" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="G32" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>Mix; chill overnight; LAN holds</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Prep Roasted Veg Stacks (→ Wed Lunch — LAN day-of)</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="F33" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="G33" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>Roast veg layers; hold warm or send hot</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>BBQ Chicken Legs (Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>Combi roast; seasoned Wk3 Sat</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>BBQ Vegan Tenders (Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>Roast</t>
         </is>
       </c>
     </row>
@@ -9839,7 +10093,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Herb Garlic Roasted Potatoes (Tue Dinner)</t>
+          <t>BBQ Chicken Legs (Tue Dinner)</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -9860,52 +10114,52 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Steam/Roast</t>
+          <t>Combi roast; seasoned Wk3 Sat</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Steam Peas &amp; Carrot (Tue Dinner side)</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>BBQ Vegan Tenders (Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F35" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="G35" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>Steam at LAN; send hot PM</t>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Roast</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -9915,7 +10169,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Vegan Nacho Mix (→ Wk1 Tue Lunch)</t>
+          <t>Herb Garlic Roasted Potatoes (Tue Dinner)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -9925,56 +10179,56 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Stove; cool; vac bag; send Thu PM cold → Rex</t>
+          <t>Steam/Roast</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Beef Nacho Mix (→ Wk1 Tue Lunch)</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>Stove; cool; vac bag; send Thu PM cold → Rex</t>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Steam Peas &amp; Carrot (Tue Dinner side)</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>Steam at LAN; send hot PM</t>
         </is>
       </c>
     </row>
@@ -9986,67 +10240,67 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>NOTE</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Marinade Five Spice Tofu</t>
+          <t>Coronation Chicken Salad (Wed Lunch)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>Rex</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr"/>
       <c r="F38" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="H38" s="6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Cold salad pre-sent; no AM run needed</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Coleslaw (→ Thu Lunch side)</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>Shred; dress; chill; send Wed PM</t>
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Vegan Nacho Mix (→ Wk1 Tue Lunch)</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Stove; cool; vac bag; send Thu PM cold → Rex</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10317,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Beef Stroganoff</t>
+          <t>Beef Nacho Mix (→ Wk1 Tue Lunch)</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -10073,16 +10327,20 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
         <v>90</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="H40" s="6" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Stove; cool; vac bag; send Thu PM cold → Rex</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -10092,12 +10350,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Vegan Mushroom Stroganoff</t>
+          <t>Marinade Five Spice Tofu</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -10107,14 +10365,14 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="H41" s="6" t="inlineStr"/>
     </row>
@@ -10131,7 +10389,7 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Prep Chickpea Salad (→ Thu Lunch)</t>
+          <t>Coleslaw (→ Thu Lunch side)</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -10141,58 +10399,54 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>Dress; chill; send Wed PM</t>
+          <t>Shred; dress; chill; send Wed PM</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Chicken Ranch Salad Mix (→ Fri Lunch — make day before send)</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>Mix; chill overnight; send Thu PM</t>
-        </is>
-      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Beef Stroganoff</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="H43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -10202,12 +10456,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Reheat Beef &amp; Vegetable Stew (Wed Dinner)</t>
+          <t>Vegan Mushroom Stroganoff</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -10221,107 +10475,103 @@
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="G44" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Prep Chickpea Salad (→ Thu Lunch)</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="G45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>Dress; chill; send Wed PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Roasted Potatoes (Wed Dinner)</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>Steam/Roast</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Reheat Eggplant/Cassava Stew (Wed Dinner)</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>Reheat</t>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Chicken Ranch Salad Mix (→ Fri Lunch — make day before send)</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>Mix; chill overnight; send Thu PM</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Halal Beef Burgers (Thu Lunch)</t>
+          <t>Reheat Beef &amp; Vegetable Stew (Wed Dinner)</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -10331,25 +10581,25 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>From freezer; oven 30 min day-of</t>
+          <t>Reheat bagged</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -10359,7 +10609,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Black Bean Patties (Thu Lunch — Veg)</t>
+          <t>Roasted Potatoes (Wed Dinner)</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -10369,35 +10619,35 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Oven or pan</t>
+          <t>Steam/Roast</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Carnitas Sauce (→ Wk. 1 Tues. Dinner)</t>
+          <t>Reheat Eggplant/Cassava Stew (Wed Dinner)</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -10411,12 +10661,16 @@
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H49" s="6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Reheat</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -10426,12 +10680,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Season Carnitas Chicken (→ Wk. 1 Tues. Dinner)</t>
+          <t>Halal Beef Burgers (Thu Lunch)</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -10441,16 +10695,20 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="H50" s="6" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>From freezer; oven 30 min day-of</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -10460,264 +10718,256 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Black Bean Patties (Thu Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Oven or pan</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Carnitas Sauce (→ Wk. 1 Tues. Dinner)</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Season Carnitas Chicken (→ Wk. 1 Tues. Dinner)</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>Season Carnitas Pork (→ Wk. 1 Tues. Dinner)</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F51" s="6" t="n">
+      <c r="F54" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="G51" s="6" t="n">
+      <c r="G54" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="H51" s="6" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Tuna Rex Salad Mix (→ Sat Lunch — make day before)</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F52" s="7" t="n">
+      <c r="F55" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G52" s="7" t="n">
+      <c r="G55" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H52" s="7" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>⚠ NO RECIPE | Mix; chill; send cold day-of</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Chickpea Rex Salad (→ Sat Lunch — make day before)</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F53" s="7" t="n">
+      <c r="F56" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G53" s="7" t="n">
+      <c r="G56" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>⚠ NO RECIPE | Dress; chill; send cold</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Prep Slaw (→ Fri Lunch)</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
-      <c r="F54" s="7" t="n">
+      <c r="F57" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G54" s="7" t="n">
+      <c r="G57" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="7" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>Shred; dress; chill; send Thu PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Teriyaki Chicken Legs (Thu Dinner)</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>Combi roast</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Chow Mein + Nappa Cabbage (Thu Dinner side)</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>Wok/oven</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Heat Falafel (frozen → oven) (Fri Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>Purchased frozen; heat day-of at Bloor</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -10727,7 +10977,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Vegan Carnitas</t>
+          <t>Teriyaki Chicken Legs (Thu Dinner)</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -10748,43 +10998,47 @@
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Stove</t>
+          <t>Combi roast</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>Broccoli Prep (Saturday Lunch)</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Chow Mein + Nappa Cabbage (Thu Dinner side)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F59" s="7" t="n">
+      <c r="F59" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="G59" s="7" t="n">
+      <c r="G59" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="H59" s="7" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Wok/oven</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -10794,12 +11048,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Prep Vegetable Biryani (→ Fri Dinner)</t>
+          <t>Heat Falafel (frozen → oven) (Fri Lunch — Veg)</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -10813,14 +11067,14 @@
         </is>
       </c>
       <c r="F60" s="6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>⚠ NO RECIPE | Chop veg; hold for oven rice</t>
+          <t>Purchased frozen; heat day-of at Bloor</t>
         </is>
       </c>
     </row>
@@ -10832,65 +11086,69 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Vegan Carnitas</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Stove</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Jerk Marinade</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G61" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H61" s="6" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>Jerk Cauliflower</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G62" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="H62" s="6" t="inlineStr"/>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Broccoli Prep (Saturday Lunch)</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="H62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -10900,12 +11158,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Reheat Tandoori Pork (Fri Dinner)</t>
+          <t>Prep Vegetable Biryani (→ Fri Dinner)</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -10915,18 +11173,18 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F63" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Reheat bagged</t>
+          <t>⚠ NO RECIPE | Chop veg; hold for oven rice</t>
         </is>
       </c>
     </row>
@@ -10938,12 +11196,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Reheat Tandoori Chicken — Halal (Fri Dinner)</t>
+          <t>Jerk Marinade</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -10953,20 +11211,16 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F64" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="H64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -10976,12 +11230,12 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Roast Tandoori Tofu (Fri Dinner — Veg)</t>
+          <t>Jerk Cauliflower</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -10991,73 +11245,69 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F65" s="6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>Oven roast</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>Tuna Salad Mix (→ NC Wk1 Mon Lunch)</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="G66" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H66" s="7" t="inlineStr">
-        <is>
-          <t>Mix; chill; send Sun PM</t>
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Reheat Tandoori Pork (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Prep Broccoli Salad (→ NC Wk1 Sun Lunch)</t>
+          <t>Reheat Tandoori Chicken — Halal (Fri Dinner)</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -11071,31 +11321,31 @@
         </is>
       </c>
       <c r="F67" s="6" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>⚠ NO RECIPE | Make at Bloor; send PM to Rex</t>
+          <t>Reheat bagged</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Trim/Season Jerk Chicken Legs (→ NC Wk1 Mon Dinner)</t>
+          <t>Roast Tandoori Tofu (Fri Dinner — Veg)</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -11105,18 +11355,18 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F68" s="6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>Season; hold in bins at Bloor</t>
+          <t>Oven roast</t>
         </is>
       </c>
     </row>
@@ -11128,33 +11378,29 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>NOTE</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Prep Roasted Veg Stacks (→ NC Wk1 Sun Lunch — Veg)</t>
+          <t>Tuna Rex + Chickpea Rex Salad (Sat Lunch)</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>Rex</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr"/>
       <c r="F69" s="6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>Slice/season at Bloor; roast Sun AM</t>
+          <t>Cold salad pre-sent Fri PM; Mixed Lettuce sent AM</t>
         </is>
       </c>
     </row>
@@ -11166,12 +11412,12 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>ALT</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>🔸 BLAND ALT — Plain Chicken Leg (3 pcs) + Naan + Stirfry Veg (NO PEANUTS) (Sat Dinner)</t>
+          <t>Tuna Salad Mix (→ NC Wk1 Mon Lunch)</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -11192,7 +11438,7 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>For no-peanuts/no-nuts restrictions (2-3 ppl)</t>
+          <t>Mix; chill; send Sun PM</t>
         </is>
       </c>
     </row>
@@ -11204,12 +11450,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Reheat Beef Massaman Curry (Sat Dinner)</t>
+          <t>Prep Broccoli Salad (→ NC Wk1 Sun Lunch)</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -11219,18 +11465,18 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F71" s="6" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>Reheat bagged</t>
+          <t>⚠ NO RECIPE | Make at Bloor; send PM to Rex</t>
         </is>
       </c>
     </row>
@@ -11242,12 +11488,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>Reheat Vegan Massaman Curry (Sat Dinner — Veg)</t>
+          <t>Trim/Season Jerk Chicken Legs (→ NC Wk1 Mon Dinner)</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -11257,18 +11503,18 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F72" s="6" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>Reheat bagged</t>
+          <t>Season; hold in bins at Bloor</t>
         </is>
       </c>
     </row>
@@ -11280,31 +11526,183 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Prep Roasted Veg Stacks (→ NC Wk1 Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>Slice/season at Bloor; roast Sun AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>ALT</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>🔸 BLAND ALT — Plain Chicken Leg (3 pcs) + Naan + Stirfry Veg (NO PEANUTS) (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>For no-peanuts/no-nuts restrictions (2-3 ppl)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Reheat Beef Massaman Curry (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Reheat Vegan Massaman Curry (Sat Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F73" s="6" t="n">
+      <c r="F77" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G73" s="6" t="n">
+      <c r="G77" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="H73" s="6" t="inlineStr"/>
+      <c r="H77" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/Labour_Report_generated.xlsx
+++ b/outputs/Labour_Report_generated.xlsx
@@ -1503,10 +1503,10 @@
       </c>
       <c r="D27" s="3" t="inlineStr"/>
       <c r="E27" s="3" t="n">
-        <v>240</v>
+        <v>155</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>240</v>
+        <v>155</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>90</v>
@@ -1515,10 +1515,10 @@
         <v>90</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>330</v>
+        <v>245</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>330</v>
+        <v>245</v>
       </c>
       <c r="K27" s="3" t="inlineStr"/>
     </row>
@@ -1538,10 +1538,10 @@
       </c>
       <c r="D28" s="3" t="inlineStr"/>
       <c r="E28" s="3" t="n">
-        <v>210</v>
+        <v>295</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>165</v>
+        <v>250</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>45</v>
@@ -1550,10 +1550,10 @@
         <v>45</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>255</v>
+        <v>340</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>210</v>
+        <v>295</v>
       </c>
       <c r="K28" s="3" t="inlineStr"/>
     </row>
@@ -1573,10 +1573,10 @@
       </c>
       <c r="D29" s="3" t="inlineStr"/>
       <c r="E29" s="3" t="n">
-        <v>185</v>
+        <v>365</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>155</v>
+        <v>335</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>120</v>
@@ -1585,10 +1585,10 @@
         <v>120</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>305</v>
+        <v>485</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>275</v>
+        <v>455</v>
       </c>
       <c r="K29" s="3" t="inlineStr"/>
     </row>
@@ -8833,7 +8833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10749,225 +10749,237 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Carnitas Sauce (→ Wk. 1 Tues. Dinner)</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Tuna Rex Salad Mix (→ Sat Lunch — make day before)</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Mix; chill; send cold day-of</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Chickpea Rex Salad (→ Sat Lunch — make day before)</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F53" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G52" s="6" t="n">
+      <c r="G53" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H52" s="6" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Dress; chill; send cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Prep Slaw (→ Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>Shred; dress; chill; send Thu PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Season Carnitas Chicken (→ Wk. 1 Tues. Dinner)</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G53" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="H53" s="6" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Teriyaki Chicken Legs (Thu Dinner)</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Combi roast</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Season Carnitas Pork (→ Wk. 1 Tues. Dinner)</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Chow Mein + Nappa Cabbage (Thu Dinner side)</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="F56" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="G54" s="6" t="n">
+      <c r="G56" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="H54" s="6" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>Tuna Rex Salad Mix (→ Sat Lunch — make day before)</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="G55" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Mix; chill; send cold day-of</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>Chickpea Rex Salad (→ Sat Lunch — make day before)</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>Wok/oven</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Heat Falafel (frozen → oven) (Fri Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F56" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G56" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Dress; chill; send cold</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>Prep Slaw (→ Fri Lunch)</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="n">
+      <c r="F57" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G57" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>Shred; dress; chill; send Thu PM</t>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Purchased frozen; heat day-of at Bloor</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -10977,7 +10989,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Teriyaki Chicken Legs (Thu Dinner)</t>
+          <t>Vegan Carnitas</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -10998,47 +11010,43 @@
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Combi roast</t>
+          <t>Stove</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Chow Mein + Nappa Cabbage (Thu Dinner side)</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Broccoli Prep (Saturday Lunch)</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F59" s="6" t="n">
+      <c r="F59" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G59" s="6" t="n">
+      <c r="G59" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>Wok/oven</t>
-        </is>
-      </c>
+      <c r="H59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -11048,12 +11056,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Heat Falafel (frozen → oven) (Fri Lunch — Veg)</t>
+          <t>Prep Vegetable Biryani (→ Fri Dinner)</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -11067,14 +11075,14 @@
         </is>
       </c>
       <c r="F60" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Purchased frozen; heat day-of at Bloor</t>
+          <t>⚠ NO RECIPE | Chop veg; hold for oven rice</t>
         </is>
       </c>
     </row>
@@ -11086,12 +11094,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Vegan Carnitas</t>
+          <t>Jerk Marinade</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -11101,54 +11109,50 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>Stove</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="H61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>Broccoli Prep (Saturday Lunch)</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="G62" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="H62" s="7" t="inlineStr"/>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Jerk Cauliflower</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -11163,7 +11167,7 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Prep Vegetable Biryani (→ Fri Dinner)</t>
+          <t>Carnitas Sauce (→ Wk. 1 Tues. Dinner)</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -11182,11 +11186,7 @@
       <c r="G63" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Chop veg; hold for oven rice</t>
-        </is>
-      </c>
+      <c r="H63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Jerk Marinade</t>
+          <t>Season Carnitas Chicken (→ Wk. 1 Tues. Dinner)</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -11211,14 +11211,14 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F64" s="6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H64" s="6" t="inlineStr"/>
     </row>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Jerk Cauliflower</t>
+          <t>Season Carnitas Pork (→ Wk. 1 Tues. Dinner)</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -11245,14 +11245,14 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F65" s="6" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="H65" s="6" t="inlineStr"/>
     </row>
@@ -11557,40 +11557,40 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>ALT</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>🔸 BLAND ALT — Plain Chicken Leg (3 pcs) + Naan + Stirfry Veg (NO PEANUTS) (Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="G74" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H74" s="7" t="inlineStr">
-        <is>
-          <t>For no-peanuts/no-nuts restrictions (2-3 ppl)</t>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Cook Carnitas Pork (→ NC Wk1 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
         </is>
       </c>
     </row>
@@ -11602,12 +11602,12 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Reheat Beef Massaman Curry (Sat Dinner)</t>
+          <t>Cook Carnitas Chicken (→ NC Wk1 Tue Dinner)</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -11621,52 +11621,52 @@
         </is>
       </c>
       <c r="F75" s="6" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>Reheat bagged</t>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>Reheat Vegan Massaman Curry (Sat Dinner — Veg)</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>ALT</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>🔸 BLAND ALT — Plain Chicken Leg (3 pcs) + Naan + Stirfry Veg (NO PEANUTS) (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>For no-peanuts/no-nuts restrictions (2-3 ppl)</t>
         </is>
       </c>
     </row>
@@ -11678,31 +11678,107 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
+          <t>Reheat Beef Massaman Curry (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Reheat Vegan Massaman Curry (Sat Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F77" s="6" t="n">
+      <c r="F79" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G77" s="6" t="n">
+      <c r="G79" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="H77" s="6" t="inlineStr"/>
+      <c r="H79" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/Labour_Report_generated.xlsx
+++ b/outputs/Labour_Report_generated.xlsx
@@ -759,10 +759,10 @@
       </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="n">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>195</v>
+        <v>270</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>60</v>
@@ -771,10 +771,10 @@
         <v>60</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>270</v>
+        <v>345</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>255</v>
+        <v>330</v>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
     </row>
@@ -794,10 +794,10 @@
       </c>
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="n">
-        <v>155</v>
+        <v>335</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>125</v>
+        <v>305</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>135</v>
@@ -806,10 +806,10 @@
         <v>135</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>290</v>
+        <v>470</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>260</v>
+        <v>440</v>
       </c>
       <c r="K8" s="3" t="inlineStr"/>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="n">
-        <v>520</v>
+        <v>640</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>625</v>
@@ -950,7 +950,7 @@
         <v>120</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>640</v>
+        <v>760</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>745</v>
@@ -1273,10 +1273,10 @@
       </c>
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="n">
-        <v>337</v>
+        <v>412</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>510</v>
+        <v>585</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
@@ -1285,10 +1285,10 @@
         <v>0</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>337</v>
+        <v>412</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>510</v>
+        <v>585</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
       </c>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="n">
-        <v>475</v>
+        <v>655</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>620</v>
+        <v>800</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>90</v>
@@ -1324,14 +1324,14 @@
         <v>90</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>565</v>
+        <v>745</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>710</v>
+        <v>890</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Oven &gt;6h</t>
+          <t>Bloor active &gt;8h | Oven &gt;6h</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3334,12 +3334,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Reheat Pork/Chicken Adobo (Fri Dinner)</t>
+          <t>Vindaloo Sauce (→ Wk. 2 Tue Dinner)</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -3349,52 +3349,56 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="6" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Stove; simmer; cool in cambro; use same day for marinade</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>Pineapple Rice (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="G48" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Oven rice</t>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Marinate Pork in Vindaloo (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
         </is>
       </c>
     </row>
@@ -3406,12 +3410,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Steam Green Beans (Fri Dinner side)</t>
+          <t>Marinate Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -3432,14 +3436,14 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Frozen; steam at Bloor</t>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -3449,7 +3453,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
+          <t>Reheat Pork/Chicken Adobo (Fri Dinner)</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -3468,64 +3472,60 @@
       <c r="G50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
+      <c r="H50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Griot Marinade</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G51" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>For Griot Pork/Chicken/Tofu</t>
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Pineapple Rice (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G51" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Oven rice</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Cut/Marinate Pork Griot</t>
+          <t>Steam Green Beans (Fri Dinner side)</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -3535,16 +3535,20 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="H52" s="6" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Frozen; steam at Bloor</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -3554,12 +3558,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Marinate Chicken Griot</t>
+          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -3569,52 +3573,56 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
         <v>15</v>
       </c>
       <c r="G53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Griot Marinade</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="H53" s="6" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="G54" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+      <c r="G54" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>For Griot Pork/Chicken/Tofu</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3639,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+          <t>Cut/Marinate Pork Griot</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -3641,94 +3649,86 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>Carrot Cabbage Fry (Sat Dinner side)</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Marinate Chicken Griot</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G56" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>Stir-fry at LAN; send hot PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
         </is>
       </c>
     </row>
@@ -3740,65 +3740,255 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
+          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Cook Pork Vindaloo (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Cook Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Carrot Cabbage Fry (Sat Dinner side)</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G61" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Stir-fry at LAN; send hot PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F58" s="6" t="n">
+      <c r="F63" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G58" s="6" t="n">
+      <c r="G63" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="H58" s="6" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="H63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>ALT</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>🔸 BLAND ALT — Plain Chicken Leg (2 pcs) + Cabbage Stirfry + Plain Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F59" s="7" t="n">
+      <c r="F64" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G59" s="7" t="n">
+      <c r="G64" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H59" s="7" t="inlineStr">
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>For bland/no-tomato/no-greens</t>
         </is>
@@ -5155,7 +5345,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Caribbean Stew</t>
+          <t>Caribbean Chicken + Chickpea Curry (→ Wk3 Tue Dinner)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -5169,7 +5359,7 @@
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>240</v>
@@ -6467,7 +6657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8633,190 +8823,380 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="G59" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Vindaloo Sauce (→ Wk. 4 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Stove; simmer; cool in cambro; use same day for marinade</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="G60" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Marinate Pork in Vindaloo (→ Wk. 4 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Marinate Chicken Vindaloo — Halal (→ Wk. 4 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="G63" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F64" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G61" s="6" t="n">
+      <c r="G64" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="H61" s="6" t="inlineStr">
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>Beef Massaman Curry (Sat Wk 4. Dinner)</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="F62" s="6" t="n">
+      <c r="F65" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="G62" s="6" t="n">
+      <c r="G65" s="6" t="n">
         <v>320</v>
       </c>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>Braised Beef (Combi) 2+ hours; Stove Top</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Cook Pork Vindaloo (→ Wk. 4 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Cook Chicken Vindaloo — Halal (→ Wk. 4 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>Potato Wedges (Sat Dinner side)</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F63" s="6" t="n">
+      <c r="F68" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="G63" s="6" t="n">
+      <c r="G68" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="H63" s="6" t="inlineStr">
+      <c r="H68" s="6" t="inlineStr">
         <is>
           <t>Purchased frozen; oven</t>
         </is>

--- a/outputs/Labour_Report_generated.xlsx
+++ b/outputs/Labour_Report_generated.xlsx
@@ -635,74 +635,82 @@
       <c r="K3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>May 19</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="n">
-        <v>303</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>333</v>
-      </c>
-      <c r="G4" s="3" t="n">
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>408</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="I4" s="3" t="n">
-        <v>378</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>408</v>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
+      <c r="I4" s="2" t="n">
+        <v>453</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>483</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Oven &gt;6h</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>May 20</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="n">
-        <v>360</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>330</v>
-      </c>
-      <c r="G5" s="3" t="n">
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n">
+        <v>540</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>510</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="I5" s="3" t="n">
-        <v>420</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>390</v>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="I5" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>570</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Bloor active &gt;8h | Oven &gt;6h</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -759,10 +767,10 @@
       </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="n">
-        <v>285</v>
+        <v>210</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>270</v>
+        <v>195</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>60</v>
@@ -771,10 +779,10 @@
         <v>60</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>345</v>
+        <v>270</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>330</v>
+        <v>255</v>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
     </row>
@@ -794,10 +802,10 @@
       </c>
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="n">
-        <v>335</v>
+        <v>155</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>305</v>
+        <v>125</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>135</v>
@@ -806,10 +814,10 @@
         <v>135</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>470</v>
+        <v>290</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>440</v>
+        <v>260</v>
       </c>
       <c r="K8" s="3" t="inlineStr"/>
     </row>
@@ -1273,10 +1281,10 @@
       </c>
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="n">
-        <v>412</v>
+        <v>337</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>585</v>
+        <v>510</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
@@ -1285,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>412</v>
+        <v>337</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>585</v>
+        <v>510</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -1312,10 +1320,10 @@
       </c>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="n">
-        <v>655</v>
+        <v>475</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>800</v>
+        <v>620</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>90</v>
@@ -1324,14 +1332,14 @@
         <v>90</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>745</v>
+        <v>565</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>890</v>
+        <v>710</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Bloor active &gt;8h | Oven &gt;6h</t>
+          <t>Oven &gt;6h</t>
         </is>
       </c>
     </row>
@@ -2572,12 +2580,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Pork Carnitas (Tue Dinner)</t>
+          <t>Vindaloo Sauce (→ Wk. 2 Tue Dinner)</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -2587,18 +2595,18 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Pork braise</t>
+          <t>Stove; simmer; cool; use same day for marinade</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2618,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Halal Chicken Carnitas (Tue Dinner)</t>
+          <t>Marinate Pork in Vindaloo (→ Wk. 2 Tue Dinner)</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -2625,59 +2633,63 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Marinate Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="G27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>Pork braise</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Steam Broccoli (Tue Dinner side)</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="n">
+      <c r="G28" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="G28" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="H28" s="7" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -2687,7 +2699,7 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Heat Crispy Chicken + Vegan Tenders (Wed Lunch)</t>
+          <t>Pork Carnitas (Tue Dinner)</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -2697,7 +2709,7 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
@@ -2708,24 +2720,24 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Frozen → oven</t>
+          <t>Pork braise</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Cook Adobo Pork/Chicken</t>
+          <t>Halal Chicken Carnitas (Tue Dinner)</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -2739,54 +2751,50 @@
         </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Oven/Combi</t>
+          <t>Pork braise</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Cook Quinoa + Shape Quinoa Cakes (→ Thu Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>Cook quinoa; combine; form cakes; chill overnight</t>
-        </is>
-      </c>
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Steam Broccoli (Tue Dinner side)</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -2796,12 +2804,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Gomen Besiga Veg Stew (→ Sat Dinner)</t>
+          <t>Heat Crispy Chicken + Vegan Tenders (Wed Lunch)</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -2811,18 +2819,18 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Stove top</t>
+          <t>Frozen → oven</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2847,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Gomen Besiga Beef Stew (→ Sat Dinner)</t>
+          <t>Cook Adobo Pork/Chicken</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -2849,52 +2857,56 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="H33" s="6" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Oven/Combi</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Bean Salad (→ Fri Lunch)</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>Dress; chill; send Thu PM</t>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Cook Quinoa + Shape Quinoa Cakes (→ Thu Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Cook quinoa; combine; form cakes; chill overnight</t>
         </is>
       </c>
     </row>
@@ -2906,12 +2918,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Reheat Chickpea Shakshuka Sauce (Wed Dinner)</t>
+          <t>Gomen Besiga Veg Stew (→ Sat Dinner)</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -2925,89 +2937,93 @@
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Reheat bagged batch</t>
+          <t>Stove top</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Herbed Couscous (Wed Dinner)</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Gomen Besiga Beef Stew (→ Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Bean Salad (→ Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F37" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="G37" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Halal Chicken Burgers (Thu Lunch)</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H37" s="6" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>Dress; chill; send Thu PM</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -3017,7 +3033,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Quinoa Burgers (Thu Lunch — Veg)</t>
+          <t>Cook Pork Vindaloo (→ Wk. 2 Tue Dinner)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -3027,25 +3043,25 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Pan fry; send hot AM</t>
+          <t>Oven; cool then vac bag; hold Bloor → send Thu PM</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -3055,7 +3071,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Vegan Chili (→ Wk2 Mon Lunch)</t>
+          <t>Cook Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -3065,31 +3081,35 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>240</v>
-      </c>
-      <c r="H39" s="6" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor → send Thu PM</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Cook Portobello Cheese Melt (→ Wk2 Sun Lunch — Veg)</t>
+          <t>Reheat Chickpea Shakshuka Sauce (Wed Dinner)</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -3099,50 +3119,54 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="H40" s="6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged batch</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Eggplant/Cassava Stew (→ Wk2 Wed Dinner)</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="H41" s="6" t="inlineStr"/>
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Herbed Couscous (Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -3152,12 +3176,12 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Reheat Butter Chicken (Thu Dinner)</t>
+          <t>Halal Chicken Burgers (Thu Lunch)</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -3167,20 +3191,16 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="H42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -3190,12 +3210,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Reheat Butter Chickpeas (Thu Dinner — Veg)</t>
+          <t>Quinoa Burgers (Thu Lunch — Veg)</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -3205,93 +3225,93 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="6" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Pan fry; send hot AM</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Roasted Cauliflower (Thu Dinner side)</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G44" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>⚠ CONFIRM carrot role in this side</t>
-        </is>
-      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Vegan Chili (→ Wk2 Mon Lunch)</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>NOTE</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Bean Salad (Fri Lunch)</t>
+          <t>Cook Portobello Cheese Melt (→ Wk2 Sun Lunch — Veg)</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Rex</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr"/>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="F45" s="6" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>Cold salad pre-sent; no AM run needed</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -3301,7 +3321,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Sausage &amp; Greens Pasta Sauce (→ Wk2 Sun Dinner)</t>
+          <t>Eggplant/Cassava Stew (→ Wk2 Wed Dinner)</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -3311,35 +3331,31 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>Stove top</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Vindaloo Sauce (→ Wk. 2 Tue Dinner)</t>
+          <t>Reheat Butter Chicken (Thu Dinner)</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -3349,35 +3365,35 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Stove; simmer; cool in cambro; use same day for marinade</t>
+          <t>Reheat bagged</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Marinate Pork in Vindaloo (→ Wk. 2 Tue Dinner)</t>
+          <t>Reheat Butter Chickpeas (Thu Dinner — Veg)</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -3387,56 +3403,52 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Roasted Cauliflower (Thu Dinner side)</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F49" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G48" s="6" t="n">
+      <c r="G49" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Marinate Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>⚠ CONFIRM carrot role in this side</t>
         </is>
       </c>
     </row>
@@ -3448,67 +3460,67 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>NOTE</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Reheat Pork/Chicken Adobo (Fri Dinner)</t>
+          <t>Bean Salad (Fri Lunch)</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>Rex</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr"/>
       <c r="F50" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="6" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Cold salad pre-sent; no AM run needed</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>Pineapple Rice (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="G51" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Oven rice</t>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Sausage &amp; Greens Pasta Sauce (→ Wk2 Sun Dinner)</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Stove top</t>
         </is>
       </c>
     </row>
@@ -3520,12 +3532,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Steam Green Beans (Fri Dinner side)</t>
+          <t>Reheat Pork/Chicken Adobo (Fri Dinner)</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -3535,73 +3547,69 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
         <v>15</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>Frozen; steam at Bloor</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Pineapple Rice (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F53" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
+      <c r="F53" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Oven rice</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Griot Marinade</t>
+          <t>Steam Green Beans (Fri Dinner side)</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -3622,7 +3630,7 @@
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>For Griot Pork/Chicken/Tofu</t>
+          <t>Frozen; steam at Bloor</t>
         </is>
       </c>
     </row>
@@ -3634,12 +3642,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Cut/Marinate Pork Griot</t>
+          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -3649,16 +3657,20 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="H55" s="6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -3673,7 +3685,7 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Marinate Chicken Griot</t>
+          <t>Griot Marinade</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -3692,45 +3704,45 @@
       <c r="G56" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="H56" s="6" t="inlineStr"/>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>For Griot Pork/Chicken/Tofu</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Cut/Marinate Pork Griot</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F57" s="7" t="n">
+      <c r="F57" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="G57" s="7" t="n">
+      <c r="G57" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
-        </is>
-      </c>
+      <c r="H57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -3745,7 +3757,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+          <t>Marinate Chicken Griot</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -3755,56 +3767,52 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Cook Pork Vindaloo (→ Wk. 2 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="G59" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="G59" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
         </is>
       </c>
     </row>
@@ -3816,12 +3824,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Cook Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
+          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -3831,18 +3839,18 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F60" s="6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4964,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Reheat bagged</t>
+          <t>Reheat bagged; pulled from Rex fridge Mon AM</t>
         </is>
       </c>
     </row>
@@ -4994,7 +5002,7 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Reheat bagged</t>
+          <t>Reheat bagged; pulled from Rex fridge Mon AM</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8823,85 +8831,85 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Vindaloo Sauce (→ Wk. 4 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G59" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>Stove; simmer; cool in cambro; use same day for marinade</t>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="G59" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Marinate Pork in Vindaloo (→ Wk. 4 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G60" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -8911,7 +8919,7 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Marinate Chicken Vindaloo — Halal (→ Wk. 4 Tue Dinner)</t>
+          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -8921,282 +8929,92 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="G62" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Beef Massaman Curry (Sat Wk 4. Dinner)</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>320</v>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Braised Beef (Combi) 2+ hours; Stove Top</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="G63" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G64" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>Beef Massaman Curry (Sat Wk 4. Dinner)</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>160</v>
-      </c>
-      <c r="G65" s="6" t="n">
-        <v>320</v>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>Braised Beef (Combi) 2+ hours; Stove Top</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>Cook Pork Vindaloo (→ Wk. 4 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="G66" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>Oven; cool then vac bag; hold Bloor fridge</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>Cook Chicken Vindaloo — Halal (→ Wk. 4 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Potato Wedges (Sat Dinner side)</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F67" s="6" t="n">
+      <c r="F63" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="G67" s="6" t="n">
+      <c r="G63" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>Oven; cool then vac bag; hold Bloor fridge</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>Potato Wedges (Sat Dinner side)</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G68" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H68" s="6" t="inlineStr">
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>Purchased frozen; oven</t>
         </is>

--- a/outputs/Labour_Report_generated.xlsx
+++ b/outputs/Labour_Report_generated.xlsx
@@ -1748,7 +1748,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>PREP ONLY — no oven. Shape, bread, freeze in blast chiller all day.</t>
+          <t>Bread, shape, blast-chill; NO oven — all hands-on</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>PREP ONLY — no oven. Shape, bread, freeze; blast chiller</t>
+          <t>Bread, shape, blast-chill; NO oven — all hands-on</t>
         </is>
       </c>
     </row>

--- a/outputs/Labour_Report_generated.xlsx
+++ b/outputs/Labour_Report_generated.xlsx
@@ -600,39 +600,43 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>May 18</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="n">
-        <v>330</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>315</v>
-      </c>
-      <c r="G3" s="3" t="n">
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n">
+        <v>405</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="I3" s="3" t="n">
-        <v>360</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>345</v>
-      </c>
-      <c r="K3" s="3" t="inlineStr"/>
+      <c r="I3" s="2" t="n">
+        <v>435</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Oven &gt;6h</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -650,10 +654,10 @@
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="n">
-        <v>378</v>
+        <v>560</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>408</v>
+        <v>590</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>75</v>
@@ -662,14 +666,14 @@
         <v>75</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>453</v>
+        <v>635</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>483</v>
+        <v>665</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Oven &gt;6h</t>
+          <t>Bloor active &gt;8h | Oven &gt;6h</t>
         </is>
       </c>
     </row>
@@ -689,10 +693,10 @@
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="n">
+        <v>570</v>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>540</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>510</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>60</v>
@@ -701,10 +705,10 @@
         <v>60</v>
       </c>
       <c r="I5" s="2" t="n">
+        <v>630</v>
+      </c>
+      <c r="J5" s="2" t="n">
         <v>600</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>570</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -767,10 +771,10 @@
       </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="n">
-        <v>210</v>
+        <v>255</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>60</v>
@@ -779,10 +783,10 @@
         <v>60</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
     </row>
@@ -1621,7 +1625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2098,12 +2102,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Cook Jerk Chicken Legs (Mon Dinner)</t>
+          <t>Vindaloo Sauce (→ Wk. 2 Tue Dinner)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -2113,18 +2117,18 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Bone-in legs; roast</t>
+          <t>Stove; simmer; cool; use same day for marinade</t>
         </is>
       </c>
     </row>
@@ -2136,12 +2140,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Jerk Cauliflower (Mon Dinner — Veg)</t>
+          <t>Marinate Pork in Vindaloo (→ Wk. 2 Tue Dinner)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -2151,18 +2155,18 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Roast</t>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2178,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Rice &amp; Beans</t>
+          <t>Marinate Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -2189,73 +2193,73 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>⚠ NO RECIPE | Oven</t>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Cabbage &amp; Carrot Stir-fry (Mon Dinner side)</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Stir-fry at LAN; send hot PM</t>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Cook Jerk Chicken Legs (Mon Dinner)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Bone-in legs; roast</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Reheat Beef Nacho Mix (Tue Lunch)</t>
+          <t>Jerk Cauliflower (Mon Dinner — Veg)</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -2265,35 +2269,35 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Reheat bagged; pulled from Rex fridge Mon AM</t>
+          <t>Roast</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Reheat Vegan Nacho Mix (Tue Lunch)</t>
+          <t>Rice &amp; Beans</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -2303,54 +2307,58 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Oven</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Cabbage &amp; Carrot Stir-fry (Mon Dinner side)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F18" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Trim/Season Shakshuka Chicken Legs (→ Wed Dinner)</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="H19" s="6" t="inlineStr"/>
+      <c r="F19" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Stir-fry at LAN; send hot PM</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -2360,12 +2368,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Adobo Marinade (→ Fri Dinner)</t>
+          <t>Reheat Beef Nacho Mix (Tue Lunch)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -2375,16 +2383,20 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H20" s="6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged; pulled from Rex fridge Mon AM</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -2394,12 +2406,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Marinate Pork/Chicken Adobo (→ Fri Dinner)</t>
+          <t>Reheat Vegan Nacho Mix (Tue Lunch)</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -2409,16 +2421,20 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" s="6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -2428,12 +2444,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Cook West African Peanut Stew Base (→ Wk2 Mon Dinner)</t>
+          <t>Trim/Season Shakshuka Chicken Legs (→ Wed Dinner)</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -2443,20 +2459,16 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Stove top braise 3hrs; reserve 12 lbs vegan BEFORE adding chicken; vac bag</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -2466,12 +2478,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Vegan Peanut Stew (→ Wk2 Mon Dinner — Veg)</t>
+          <t>Adobo Marinade (→ Fri Dinner)</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -2481,94 +2493,90 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>(incl. above)</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>Reserved from base stew before chicken added; vac bag separately</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="H23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Tomato Cucumber Salad (→ Thu Lunch)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>Mix; chill; send Wed PM</t>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Cut &amp; Marinate Pork for Adobo (→ Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Cut pork; coat in Adobo Marinade; chill overnight</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Prep Chiffonade Lettuce &amp; Sliced Peppers (→ Wed Lunch)</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>Prep at LAN; send cold Wed AM</t>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Marinate Chicken for Adobo — Halal (→ Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Coat in Adobo Marinade; chill overnight</t>
         </is>
       </c>
     </row>
@@ -2580,12 +2588,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Vindaloo Sauce (→ Wk. 2 Tue Dinner)</t>
+          <t>Cook West African Peanut Stew Base (→ Wk2 Mon Dinner)</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -2595,18 +2603,18 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Stove; simmer; cool; use same day for marinade</t>
+          <t>Stove top braise 3hrs; reserve 12 lbs vegan BEFORE adding chicken; vac bag</t>
         </is>
       </c>
     </row>
@@ -2618,109 +2626,109 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Vegan Peanut Stew (→ Wk2 Mon Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>(incl. above)</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Reserved from base stew before chicken added; vac bag separately</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Marinate Pork in Vindaloo (→ Wk. 2 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Tomato Cucumber Salad (→ Thu Lunch)</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F28" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G28" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Mix; chill; send Wed PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Marinate Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Pork Carnitas (Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>Pork braise</t>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Prep Chiffonade Lettuce &amp; Sliced Peppers (→ Wed Lunch)</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>Prep at LAN; send cold Wed AM</t>
         </is>
       </c>
     </row>
@@ -2732,12 +2740,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Halal Chicken Carnitas (Tue Dinner)</t>
+          <t>Cook Pork Vindaloo (→ Wk. 2 Tue Dinner)</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -2747,59 +2755,63 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor → send Wed PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Cook Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F30" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>Pork braise</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Steam Broccoli (Tue Dinner side)</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="H31" s="7" t="inlineStr"/>
+      <c r="F31" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor → send Wed PM</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -2809,7 +2821,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Heat Crispy Chicken + Vegan Tenders (Wed Lunch)</t>
+          <t>Pork Carnitas (Tue Dinner)</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -2819,7 +2831,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
@@ -2830,24 +2842,24 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Frozen → oven</t>
+          <t>Pork braise</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Cook Adobo Pork/Chicken</t>
+          <t>Halal Chicken Carnitas (Tue Dinner)</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -2861,54 +2873,50 @@
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Oven/Combi</t>
+          <t>Pork braise</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Cook Quinoa + Shape Quinoa Cakes (→ Thu Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>Cook quinoa; combine; form cakes; chill overnight</t>
-        </is>
-      </c>
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Steam Broccoli (Tue Dinner side)</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -2918,12 +2926,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Gomen Besiga Veg Stew (→ Sat Dinner)</t>
+          <t>Heat Crispy Chicken + Vegan Tenders (Wed Lunch)</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -2933,18 +2941,18 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Stove top</t>
+          <t>Frozen → oven</t>
         </is>
       </c>
     </row>
@@ -2956,12 +2964,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Gomen Besiga Beef Stew (→ Sat Dinner)</t>
+          <t>Cook Quinoa + Shape Quinoa Cakes (→ Thu Lunch — Veg)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -2971,52 +2979,56 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="H36" s="6" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Cook quinoa; combine; form cakes; chill overnight</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Bean Salad (→ Fri Lunch)</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G37" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>Dress; chill; send Thu PM</t>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Gomen Besiga Veg Stew (→ Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Stove top</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3045,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Cook Pork Vindaloo (→ Wk. 2 Tue Dinner)</t>
+          <t>Gomen Besiga Beef Stew (→ Sat Dinner)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -3052,47 +3064,43 @@
       <c r="G38" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>Oven; cool then vac bag; hold Bloor → send Thu PM</t>
-        </is>
-      </c>
+      <c r="H38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Cook Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G39" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>Oven; cool then vac bag; hold Bloor → send Thu PM</t>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Bean Salad (→ Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>Dress; chill; send Thu PM</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3112,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Reheat Chickpea Shakshuka Sauce (Wed Dinner)</t>
+          <t>Cook Pork Adobo (→ Fri Dinner)</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -3119,59 +3127,63 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Oven/Combi; cool; vac bag</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Cook Chicken Adobo — Halal (→ Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F40" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>Reheat bagged batch</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Herbed Couscous (Wed Dinner)</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G41" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H41" s="7" t="inlineStr"/>
+      <c r="F41" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Oven/Combi; cool; vac bag</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -3181,7 +3193,7 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Halal Chicken Burgers (Thu Lunch)</t>
+          <t>Roast Shakshuka Chicken Legs (Wed Dinner)</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -3191,31 +3203,35 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H42" s="6" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>⚠ CONFIRM qty/hotels | Same-day roast at Bloor</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Quinoa Burgers (Thu Lunch — Veg)</t>
+          <t>Reheat Chickpea Shakshuka Sauce (Wed Dinner)</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -3225,54 +3241,54 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Pan fry; send hot AM</t>
+          <t>Reheat bagged batch</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Vegan Chili (→ Wk2 Mon Lunch)</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="G44" s="6" t="n">
-        <v>240</v>
-      </c>
-      <c r="H44" s="6" t="inlineStr"/>
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Herbed Couscous (Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -3287,7 +3303,7 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Cook Portobello Cheese Melt (→ Wk2 Sun Lunch — Veg)</t>
+          <t>Halal Chicken Burgers (Thu Lunch)</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -3297,14 +3313,14 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H45" s="6" t="inlineStr"/>
     </row>
@@ -3321,7 +3337,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Eggplant/Cassava Stew (→ Wk2 Wed Dinner)</t>
+          <t>Quinoa Burgers (Thu Lunch — Veg)</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -3331,16 +3347,20 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="H46" s="6" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Pan fry; send hot AM</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -3350,12 +3370,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Reheat Butter Chicken (Thu Dinner)</t>
+          <t>Vegan Chili (→ Wk2 Mon Lunch)</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -3365,20 +3385,16 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>240</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="H47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -3388,12 +3404,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Reheat Butter Chickpeas (Thu Dinner — Veg)</t>
+          <t>Cook Portobello Cheese Melt (→ Wk2 Sun Lunch — Veg)</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -3403,196 +3419,192 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>Roasted Cauliflower (Thu Dinner side)</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G49" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>⚠ CONFIRM carrot role in this side</t>
-        </is>
-      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Eggplant/Cassava Stew (→ Wk2 Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>NOTE</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Bean Salad (Fri Lunch)</t>
+          <t>Reheat Butter Chicken (Thu Dinner)</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Rex</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr"/>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="F50" s="6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Cold salad pre-sent; no AM run needed</t>
+          <t>Reheat bagged</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Reheat Butter Chickpeas (Thu Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Roasted Cauliflower (Thu Dinner side)</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>⚠ CONFIRM carrot role in this side</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Sausage &amp; Greens Pasta Sauce (→ Wk2 Sun Dinner)</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="G51" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>Stove top</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Reheat Pork/Chicken Adobo (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G52" s="6" t="n">
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Bean Salad (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Rex</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="6" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>Pineapple Rice (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="G53" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Oven rice</t>
+      <c r="G53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Cold salad pre-sent; no AM run needed</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3621,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Steam Green Beans (Fri Dinner side)</t>
+          <t>Sausage &amp; Greens Pasta Sauce (→ Wk2 Sun Dinner)</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -3619,73 +3631,73 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Frozen; steam at Bloor</t>
+          <t>Stove top</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Pineapple Rice (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F55" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
+      <c r="F55" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Oven rice</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Griot Marinade</t>
+          <t>Steam Green Beans (Fri Dinner side)</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -3706,24 +3718,24 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>For Griot Pork/Chicken/Tofu</t>
+          <t>Frozen; steam at Bloor</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Cut/Marinate Pork Griot</t>
+          <t>Reheat Pork Adobo (Fri Dinner)</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -3733,31 +3745,31 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Marinate Chicken Griot</t>
+          <t>Reheat Halal Chicken Adobo (Fri Dinner)</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -3767,52 +3779,52 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F58" s="6" t="n">
         <v>15</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="G59" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Roast Adobo Tofu (Fri Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>⚠ CONFIRM cook time | Same-day roast at Bloor</t>
         </is>
       </c>
     </row>
@@ -3824,71 +3836,71 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G60" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>Carrot Cabbage Fry (Sat Dinner side)</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G61" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>Stir-fry at LAN; send hot PM</t>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Griot Marinade</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>For Griot Pork/Chicken/Tofu</t>
         </is>
       </c>
     </row>
@@ -3900,12 +3912,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
+          <t>Cut/Marinate Pork Griot</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -3915,20 +3927,16 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F62" s="6" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -3938,12 +3946,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Rice (Sat Dinner)</t>
+          <t>Marinate Chicken Griot</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -3953,14 +3961,14 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F63" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H63" s="6" t="inlineStr"/>
     </row>
@@ -3972,31 +3980,217 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Carrot Cabbage Fry (Sat Dinner side)</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Stir-fry at LAN; send hot PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Rice (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H68" s="6" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
           <t>ALT</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>🔸 BLAND ALT — Plain Chicken Leg (2 pcs) + Cabbage Stirfry + Plain Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F64" s="7" t="n">
+      <c r="F69" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G64" s="7" t="n">
+      <c r="G69" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H64" s="7" t="inlineStr">
+      <c r="H69" s="7" t="inlineStr">
         <is>
           <t>For bland/no-tomato/no-greens</t>
         </is>

--- a/outputs/Labour_Report_generated.xlsx
+++ b/outputs/Labour_Report_generated.xlsx
@@ -950,10 +950,10 @@
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="n">
-        <v>640</v>
+        <v>700</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>625</v>
+        <v>685</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>120</v>
@@ -962,10 +962,10 @@
         <v>120</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>760</v>
+        <v>820</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>745</v>
+        <v>805</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6061,7 +6061,7 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Beef Sausages (Thu Dinner)</t>
+          <t>Refried Beans (→ Fri Dinner side)</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -6081,18 +6081,18 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Cook sausages for dinner service</t>
+          <t>⚠ NO RECIPE | ⚠ CONFIRM cook time</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Halal Sausages (Thu Dinner)</t>
+          <t>Beef Sausages (Thu Dinner)</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Vegan Sausages (Thu Dinner)</t>
+          <t>Halal Sausages (Thu Dinner)</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>HOT Peas &amp; Carrot → Dinner side</t>
+          <t>Vegan Sausages (Thu Dinner)</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -6195,18 +6195,18 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Combi</t>
+          <t>Cook sausages for dinner service</t>
         </is>
       </c>
     </row>
@@ -6218,12 +6218,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Reheat Gravy (Thu Dinner + hold portion for Sat Dinner Meatloaf)</t>
+          <t>HOT Peas &amp; Carrot → Dinner side</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -6233,25 +6233,25 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Reheat bagged; portion ½ for Thu PM, hold ½ at Bloor for Sat</t>
+          <t>Combi</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Heat Falafel (frozen → oven) (Fri Lunch — Veg)</t>
+          <t>Reheat Gravy (Thu Dinner + hold portion for Sat Dinner Meatloaf)</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>Purchased frozen; heat day-of at Bloor</t>
+          <t>Reheat bagged; portion ½ for Thu PM, hold ½ at Bloor for Sat</t>
         </is>
       </c>
     </row>
@@ -6294,12 +6294,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Beef CONC Salad Mix (→ Wk3 Sat Lunch)</t>
+          <t>Heat Falafel (frozen → oven) (Fri Lunch — Veg)</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -6309,18 +6309,18 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Cook; send Rex Sat PM; pull Wk3 Fri AM</t>
+          <t>Purchased frozen; heat day-of at Bloor</t>
         </is>
       </c>
     </row>
@@ -6337,104 +6337,104 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
+          <t>Beef CONC Salad Mix (→ Wk3 Sat Lunch)</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Cook; send Rex Sat PM; pull Wk3 Fri AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
           <t>Vegan CONC Salad Mix (→ Wk3 Sat Lunch)</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F58" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G57" s="6" t="n">
+      <c r="G58" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>Cook; send Rex Sat PM; pull Wk3 Fri AM</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Prep Butternut Squash (→ Sat Dinner side)</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F58" s="7" t="n">
+      <c r="F59" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G58" s="7" t="n">
+      <c r="G59" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="H58" s="7" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>Peel/dice at LAN; chill overnight</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Prep &amp; Tray Meatloaf (raw) — 7 Beef (→ Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="G59" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Prep &amp; Tray Vegan Meatloaf (raw) — (→ Sat Dinner)</t>
+          <t>Prep &amp; Tray Meatloaf (raw) — 7 Beef (→ Sat Dinner)</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -6461,14 +6461,14 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F60" s="6" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
@@ -6484,12 +6484,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Reheat Refried Beans (Fri Dinner side)</t>
+          <t>Prep &amp; Tray Vegan Meatloaf (raw) — (→ Sat Dinner)</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -6503,14 +6503,14 @@
         </is>
       </c>
       <c r="F61" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>⚠ NO RECIPE — Reheat bagged</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
     </row>
@@ -6522,12 +6522,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Arroz con Pollo</t>
+          <t>Reheat Refried Beans (Fri Dinner side)</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -6537,90 +6537,90 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F62" s="6" t="n">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>⚠ NO RECIPE — Reheat bagged</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Arroz con Pollo</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>Tuna Rex + Chickpea Rex Salad (Sat Lunch)</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr"/>
-      <c r="F63" s="6" t="n">
+      <c r="E64" s="6" t="inlineStr"/>
+      <c r="F64" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G63" s="6" t="n">
+      <c r="G64" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="6" t="inlineStr">
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>Cold salad pre-sent; no AM run needed</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>Prep Roasted Peppers &amp; Onions (→ Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="G64" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
         </is>
       </c>
     </row>
@@ -6637,66 +6637,66 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
+          <t>Prep Roasted Peppers &amp; Onions (→ Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
           <t>Tuna Salad Mix (→ Wk3 Mon Lunch)</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F65" s="7" t="n">
+      <c r="F66" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G65" s="7" t="n">
+      <c r="G66" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="H66" s="7" t="inlineStr">
         <is>
           <t>Mix; chill; send Sun PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>Prep Broccoli Salad (→ Wk3 Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="G66" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Make at Bloor; send PM to Rex</t>
         </is>
       </c>
     </row>
@@ -6708,12 +6708,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Beef Meatloaf — Bake (Sat Dinner)</t>
+          <t>Prep Broccoli Salad (→ Wk3 Sun Lunch)</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -6723,18 +6723,18 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F67" s="6" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>Bake meatloaf from tray</t>
+          <t>⚠ NO RECIPE | Make at Bloor; send PM to Rex</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Vegan Meatloaf — Bake (Sat Dinner)</t>
+          <t>Beef Meatloaf — Bake (Sat Dinner)</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -6770,7 +6770,11 @@
       <c r="G68" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="H68" s="6" t="inlineStr"/>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>Bake meatloaf from tray</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -6785,7 +6789,7 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Roasted Potatoes (Sat Dinner)</t>
+          <t>Vegan Meatloaf — Bake (Sat Dinner)</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -6804,45 +6808,79 @@
       <c r="G69" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="H69" s="6" t="inlineStr">
+      <c r="H69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Roasted Potatoes (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="7" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>Roasted Butternut Squash (Sat Dinner side)</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F70" s="7" t="n">
+      <c r="F71" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G70" s="7" t="n">
+      <c r="G71" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="H70" s="7" t="inlineStr">
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>Roast at LAN day-of</t>
         </is>

--- a/outputs/Labour_Report_generated.xlsx
+++ b/outputs/Labour_Report_generated.xlsx
@@ -699,16 +699,16 @@
         <v>540</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I5" s="2" t="n">
+        <v>660</v>
+      </c>
+      <c r="J5" s="2" t="n">
         <v>630</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>600</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3100,47 +3100,43 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>Dress; chill; send Thu PM</t>
+          <t>Dress; chill; send Thu PM | ⚠ NO RECIPE</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Cook Pork Adobo (→ Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="G40" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>Oven/Combi; cool; vac bag</t>
-        </is>
-      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Egg Salad Mix (→ Fri Lunch — make at LAN)</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -3155,7 +3151,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Cook Chicken Adobo — Halal (→ Fri Dinner)</t>
+          <t>Cook Pork Adobo (→ Fri Dinner)</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -3165,14 +3161,14 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
@@ -3193,7 +3189,7 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Roast Shakshuka Chicken Legs (Wed Dinner)</t>
+          <t>Cook Chicken Adobo — Halal (→ Fri Dinner)</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -3203,18 +3199,18 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>⚠ CONFIRM qty/hotels | Same-day roast at Bloor</t>
+          <t>Oven/Combi; cool; vac bag</t>
         </is>
       </c>
     </row>
@@ -3226,103 +3222,107 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Roast Shakshuka Chicken Legs (Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>⚠ CONFIRM qty/hotels | Same-day roast at Bloor</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>Reheat Chickpea Shakshuka Sauce (Wed Dinner)</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F44" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="G44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="6" t="inlineStr">
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>Reheat bagged batch</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>Herbed Couscous (Wed Dinner)</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F45" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G45" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H44" s="7" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Halal Chicken Burgers (Thu Lunch)</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H45" s="6" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Quinoa Burgers (Thu Lunch — Veg)</t>
+          <t>Halal Chicken Burgers (Thu Lunch)</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -3347,20 +3347,16 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>Pan fry; send hot AM</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -3375,7 +3371,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Vegan Chili (→ Wk2 Mon Lunch)</t>
+          <t>Quinoa Burgers (Thu Lunch — Veg)</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -3385,16 +3381,20 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>240</v>
-      </c>
-      <c r="H47" s="6" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Pan fry; send hot AM</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Cook Portobello Cheese Melt (→ Wk2 Sun Lunch — Veg)</t>
+          <t>Vegan Chili (→ Wk2 Mon Lunch)</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -3419,14 +3419,14 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>240</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>45</v>
+        <v>240</v>
       </c>
       <c r="H48" s="6" t="inlineStr"/>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Eggplant/Cassava Stew (→ Wk2 Wed Dinner)</t>
+          <t>Cook Portobello Cheese Melt (→ Wk2 Sun Lunch — Veg)</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -3453,14 +3453,14 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="H49" s="6" t="inlineStr"/>
     </row>
@@ -3472,12 +3472,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Reheat Butter Chicken (Thu Dinner)</t>
+          <t>Eggplant/Cassava Stew (→ Wk2 Wed Dinner)</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -3487,20 +3487,16 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -3515,7 +3511,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Reheat Butter Chickpeas (Thu Dinner — Veg)</t>
+          <t>Reheat Butter Chicken (Thu Dinner)</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -3534,77 +3530,81 @@
       <c r="G51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Reheat Butter Chickpeas (Thu Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Roasted Cauliflower (Thu Dinner side)</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F52" s="7" t="n">
+      <c r="F53" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G52" s="7" t="n">
+      <c r="G53" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H52" s="7" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>⚠ CONFIRM carrot role in this side</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Bean Salad (Fri Lunch)</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>Rex</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr"/>
-      <c r="F53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>Cold salad pre-sent; no AM run needed</t>
         </is>
       </c>
     </row>
@@ -3616,109 +3616,105 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>NOTE</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
+          <t>Egg Salad Wrap + Bean Salad (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Rex</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>Cold salad pre-sent; no AM run needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
           <t>Sausage &amp; Greens Pasta Sauce (→ Wk2 Sun Dinner)</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="F55" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="G54" s="6" t="n">
+      <c r="G55" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>Stove top</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Pineapple Rice (Fri Dinner)</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F55" s="7" t="n">
+      <c r="F56" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G55" s="7" t="n">
+      <c r="G56" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>⚠ NO RECIPE | Oven rice</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Steam Green Beans (Fri Dinner side)</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>Frozen; steam at Bloor</t>
         </is>
       </c>
     </row>
@@ -3730,12 +3726,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Reheat Pork Adobo (Fri Dinner)</t>
+          <t>Steam Green Beans (Fri Dinner side)</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -3745,16 +3741,20 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
         <v>15</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="6" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Frozen; steam at Bloor</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Reheat Halal Chicken Adobo (Fri Dinner)</t>
+          <t>Reheat Pork Adobo (Fri Dinner)</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F58" s="6" t="n">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Roast Adobo Tofu (Fri Dinner — Veg)</t>
+          <t>Reheat Halal Chicken Adobo (Fri Dinner)</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -3813,35 +3813,31 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F59" s="6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>⚠ CONFIRM cook time | Same-day roast at Bloor</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>HEAT</t>
+          <t>COOK</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
+          <t>Roast Adobo Tofu (Fri Dinner — Veg)</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -3851,18 +3847,18 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F60" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Reheat bagged</t>
+          <t>⚠ CONFIRM cook time | Same-day roast at Bloor</t>
         </is>
       </c>
     </row>
@@ -3874,12 +3870,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Griot Marinade</t>
+          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -3889,18 +3885,18 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
         <v>15</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>For Griot Pork/Chicken/Tofu</t>
+          <t>Reheat bagged</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3913,7 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Cut/Marinate Pork Griot</t>
+          <t>Griot Marinade</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -3927,16 +3923,20 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F62" s="6" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="H62" s="6" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>For Griot Pork/Chicken/Tofu</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -3951,176 +3951,172 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
+          <t>Cut/Marinate Pork Griot</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="H63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
           <t>Marinate Chicken Griot</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F63" s="6" t="n">
+      <c r="F64" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="G63" s="6" t="n">
+      <c r="G64" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="H63" s="6" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="H64" s="6" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F64" s="7" t="n">
+      <c r="F65" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G64" s="7" t="n">
+      <c r="G65" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="H64" s="7" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F65" s="6" t="n">
+      <c r="F66" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G65" s="6" t="n">
+      <c r="G66" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="H65" s="6" t="inlineStr">
+      <c r="H66" s="6" t="inlineStr">
         <is>
           <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>Carrot Cabbage Fry (Sat Dinner side)</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F66" s="7" t="n">
+      <c r="F67" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G66" s="7" t="n">
+      <c r="G67" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H66" s="7" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>Stir-fry at LAN; send hot PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
         </is>
       </c>
     </row>
@@ -4132,65 +4128,103 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>HEAT</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
+          <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F68" s="6" t="n">
+      <c r="F69" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G68" s="6" t="n">
+      <c r="G69" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="H68" s="6" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="inlineStr">
+      <c r="H69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>ALT</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>🔸 BLAND ALT — Plain Chicken Leg (2 pcs) + Cabbage Stirfry + Plain Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F69" s="7" t="n">
+      <c r="F70" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="G69" s="7" t="n">
+      <c r="G70" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H69" s="7" t="inlineStr">
+      <c r="H70" s="7" t="inlineStr">
         <is>
           <t>For bland/no-tomato/no-greens</t>
         </is>
@@ -8068,7 +8102,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>Prep at LAN; send Thu PM</t>
+          <t>Prep at LAN; send Thu PM | ⚠ NO RECIPE</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8635,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Bean Salad (Fri Lunch)</t>
+          <t>Egg Salad Wrap + Bean Salad (Fri Lunch)</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">

--- a/outputs/Labour_Report_generated.xlsx
+++ b/outputs/Labour_Report_generated.xlsx
@@ -699,16 +699,16 @@
         <v>540</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -732,10 +732,10 @@
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="n">
-        <v>365</v>
+        <v>395</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -744,10 +744,10 @@
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>485</v>
+        <v>515</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -3105,38 +3105,38 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Egg Salad Mix (→ Fri Lunch — make at LAN)</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F40" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="G40" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="H40" s="7" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">

--- a/outputs/Labour_Report_generated.xlsx
+++ b/outputs/Labour_Report_generated.xlsx
@@ -1281,10 +1281,10 @@
       </c>
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -8897,16 +8897,20 @@
           <t>Bloor</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr"/>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="F50" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Vegan portion pulled before chicken added; shares cook time</t>
+          <t>Vegan portion pulled before chicken added; shares cook time with Chicken Chili</t>
         </is>
       </c>
     </row>
